--- a/20260702黄冈社会实践10天日程安排草表.xlsx
+++ b/20260702黄冈社会实践10天日程安排草表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ants\Desktop\社会实践\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DE5888-4E73-4BE5-BCCB-20DF4A20C272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70739925-9C53-4B7E-BC5D-73C37285AE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11596" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="141">
   <si>
     <t>黄冈武穴社会实践 10 天日程安排</t>
   </si>
@@ -452,15 +452,19 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>返程时间待定</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>上海出发赴九江K1556（10.13-22:15）</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>九江接站前往四望镇；（22:15-00:00）（13986545575）</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>\</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>武昌出发赴上海松江K121（30日19:05-31日10:14）</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -1012,7 +1016,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -1029,7 +1033,7 @@
         <v>133</v>
       </c>
       <c r="M3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="72" customHeight="1">
@@ -1053,13 +1057,16 @@
       <c r="L4" s="10" t="s">
         <v>132</v>
       </c>
+      <c r="M4" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="5" spans="1:14" ht="72" customHeight="1">
       <c r="A5" s="9" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -1074,6 +1081,9 @@
       </c>
       <c r="L5" s="10" t="s">
         <v>135</v>
+      </c>
+      <c r="M5" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="58.05" customHeight="1">
